--- a/cet4/result/27_校园初恋_那年夏天的甜蜜时光/27_校园初恋_那年夏天的甜蜜时光_学习版.xlsx
+++ b/cet4/result/27_校园初恋_那年夏天的甜蜜时光/27_校园初恋_那年夏天的甜蜜时光_学习版.xlsx
@@ -397,619 +397,465 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D32"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>department</v>
       </c>
       <c r="B2" t="str">
-        <v>department</v>
+        <v>/dɪˈpɑːrtmənt/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>系</v>
       </c>
-      <c r="D2" t="str">
-        <v>department(系)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>term</v>
       </c>
       <c r="B3" t="str">
-        <v>term</v>
+        <v>/tɜːrm/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D3" t="str">
         <v>学期</v>
       </c>
-      <c r="D3" t="str">
-        <v>term(学期)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>pillar</v>
       </c>
       <c r="B4" t="str">
-        <v>pillar</v>
+        <v>/ˈpɪlər/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D4" t="str">
         <v>柱子</v>
       </c>
-      <c r="D4" t="str">
-        <v>pillar(柱子)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>everywhere</v>
       </c>
       <c r="B5" t="str">
-        <v>everywhere</v>
+        <v>/ˈevriwer/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>到处</v>
       </c>
-      <c r="D5" t="str">
-        <v>everywhere(到处)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>turning</v>
       </c>
       <c r="B6" t="str">
-        <v>turning</v>
+        <v>/ˈtɜːrnɪŋ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D6" t="str">
         <v>转弯</v>
       </c>
-      <c r="D6" t="str">
-        <v>turning(转弯)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>glance</v>
       </c>
       <c r="B7" t="str">
-        <v>glance</v>
+        <v>/ɡlæns/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vi.</v>
+      </c>
+      <c r="D7" t="str">
         <v>一瞥</v>
       </c>
-      <c r="D7" t="str">
-        <v>glance(一瞥)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>intensive</v>
       </c>
       <c r="B8" t="str">
-        <v>intensive</v>
+        <v>/ɪnˈtensɪv/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>加强的</v>
       </c>
-      <c r="D8" t="str">
-        <v>intensive(加强的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>theory</v>
       </c>
       <c r="B9" t="str">
-        <v>theory</v>
+        <v>/ˈθiːəri,ˈθɪri/</v>
       </c>
       <c r="C9" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>理论</v>
       </c>
-      <c r="D9" t="str">
-        <v>theory(理论)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>conversation</v>
       </c>
       <c r="B10" t="str">
-        <v>conversation</v>
+        <v>/ˌkɑːnvərˈseɪʃn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>对话</v>
       </c>
-      <c r="D10" t="str">
-        <v>conversation(对话)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>fine</v>
       </c>
       <c r="B11" t="str">
-        <v>theory</v>
+        <v>/faɪn/</v>
       </c>
       <c r="C11" t="str">
-        <v>理论</v>
+        <v>n./vt./v./adj./adv.</v>
       </c>
       <c r="D11" t="str">
-        <v>theory(理论)📢</v>
+        <v>好的</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>transport</v>
       </c>
       <c r="B12" t="str">
-        <v>fine</v>
+        <v>/ˈtrænspɔːrt/</v>
       </c>
       <c r="C12" t="str">
-        <v>好的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D12" t="str">
-        <v>fine(好的)📢</v>
+        <v>运输</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>move</v>
       </c>
       <c r="B13" t="str">
-        <v>transport</v>
+        <v>/muːv/</v>
       </c>
       <c r="C13" t="str">
-        <v>运输</v>
+        <v>n./v.</v>
       </c>
       <c r="D13" t="str">
-        <v>transport(运输)📢</v>
+        <v>移动</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>mat</v>
       </c>
       <c r="B14" t="str">
-        <v>move</v>
+        <v>/mæt/</v>
       </c>
       <c r="C14" t="str">
-        <v>移动</v>
+        <v>n./v.</v>
       </c>
       <c r="D14" t="str">
-        <v>move(移动)📢</v>
+        <v>垫子</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>logic</v>
       </c>
       <c r="B15" t="str">
-        <v>mat</v>
+        <v>/ˈlɑːdʒɪk/</v>
       </c>
       <c r="C15" t="str">
-        <v>垫子</v>
+        <v>n.</v>
       </c>
       <c r="D15" t="str">
-        <v>mat(垫子)📢</v>
+        <v>逻辑</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>problem</v>
       </c>
       <c r="B16" t="str">
-        <v>logic</v>
+        <v>/ˈprɑːbləm/</v>
       </c>
       <c r="C16" t="str">
-        <v>逻辑</v>
+        <v>n./adj.</v>
       </c>
       <c r="D16" t="str">
-        <v>logic(逻辑)📢</v>
+        <v>问题</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>noisy</v>
       </c>
       <c r="B17" t="str">
-        <v>problem</v>
+        <v>/ˈnɔɪzi/</v>
       </c>
       <c r="C17" t="str">
-        <v>问题</v>
+        <v>adj.</v>
       </c>
       <c r="D17" t="str">
-        <v>problem(问题)📢</v>
+        <v>嘈杂</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>hesitate</v>
       </c>
       <c r="B18" t="str">
-        <v>noisy</v>
+        <v>/ˈhezɪteɪt/</v>
       </c>
       <c r="C18" t="str">
-        <v>嘈杂</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D18" t="str">
-        <v>noisy(嘈杂)📢</v>
+        <v>犹豫</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>beat</v>
       </c>
       <c r="B19" t="str">
-        <v>hesitate</v>
+        <v>/biːt/</v>
       </c>
       <c r="C19" t="str">
-        <v>犹豫</v>
+        <v>n./v.</v>
       </c>
       <c r="D19" t="str">
-        <v>hesitate(犹豫)📢</v>
+        <v>拍子</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>slight</v>
       </c>
       <c r="B20" t="str">
-        <v>beat</v>
+        <v>/slaɪt/</v>
       </c>
       <c r="C20" t="str">
-        <v>拍子</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>beat(拍子)📢</v>
+        <v>轻微的</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>development</v>
       </c>
       <c r="B21" t="str">
-        <v>slight</v>
+        <v>/dɪˈveləpmənt/</v>
       </c>
       <c r="C21" t="str">
-        <v>轻微的</v>
+        <v>n.</v>
       </c>
       <c r="D21" t="str">
-        <v>slight(轻微的)📢</v>
+        <v>发展</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>thorough</v>
       </c>
       <c r="B22" t="str">
-        <v>development</v>
+        <v>/ˈθɜːroʊ/</v>
       </c>
       <c r="C22" t="str">
-        <v>发展</v>
+        <v>adj.</v>
       </c>
       <c r="D22" t="str">
-        <v>development(发展)📢</v>
+        <v>彻底的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>flexible</v>
       </c>
       <c r="B23" t="str">
-        <v>thorough</v>
+        <v>/ˈfleksəbl/</v>
       </c>
       <c r="C23" t="str">
-        <v>彻底的</v>
+        <v>adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>thorough(彻底的)📢</v>
+        <v>灵活的</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>barrier</v>
       </c>
       <c r="B24" t="str">
-        <v>problem</v>
+        <v>/ˈbæriər/</v>
       </c>
       <c r="C24" t="str">
-        <v>问题</v>
+        <v>n./vt.</v>
       </c>
       <c r="D24" t="str">
-        <v>problem(问题)📢</v>
+        <v>障碍</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>hardly</v>
       </c>
       <c r="B25" t="str">
-        <v>flexible</v>
+        <v>/ˈhɑːrdli/</v>
       </c>
       <c r="C25" t="str">
-        <v>灵活的</v>
+        <v>v./adv.</v>
       </c>
       <c r="D25" t="str">
-        <v>flexible(灵活的)📢</v>
+        <v>几乎不</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>sorrow</v>
       </c>
       <c r="B26" t="str">
-        <v>logic</v>
+        <v>/ˈsɑːroʊ/</v>
       </c>
       <c r="C26" t="str">
-        <v>逻辑</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>logic(逻辑)📢</v>
+        <v>悲伤</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>shock</v>
       </c>
       <c r="B27" t="str">
-        <v>glance</v>
+        <v>/ʃɑːk/</v>
       </c>
       <c r="C27" t="str">
-        <v>一瞥</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>glance(一瞥)📢</v>
+        <v>震惊</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>propose</v>
       </c>
       <c r="B28" t="str">
-        <v>problem</v>
+        <v>/prəˈpoʊz/</v>
       </c>
       <c r="C28" t="str">
-        <v>问题</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>problem(问题)📢</v>
+        <v>提议</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>compass</v>
       </c>
       <c r="B29" t="str">
-        <v>barrier</v>
+        <v>/ˈkʌmpəs/</v>
       </c>
       <c r="C29" t="str">
-        <v>障碍</v>
+        <v>n./vt.</v>
       </c>
       <c r="D29" t="str">
-        <v>barrier(障碍)📢</v>
+        <v>指南针</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>witness</v>
       </c>
       <c r="B30" t="str">
-        <v>hardly</v>
+        <v>/ˈwɪtnəs/</v>
       </c>
       <c r="C30" t="str">
-        <v>几乎不</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>hardly(几乎不)📢</v>
+        <v>见证</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>until</v>
       </c>
       <c r="B31" t="str">
-        <v>sorrow</v>
+        <v>/ənˈtɪl/</v>
       </c>
       <c r="C31" t="str">
-        <v>悲伤</v>
+        <v>prep./conj.</v>
       </c>
       <c r="D31" t="str">
-        <v>sorrow(悲伤)📢</v>
+        <v>直到</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>crowd</v>
       </c>
       <c r="B32" t="str">
-        <v>shock</v>
+        <v>/kraʊd/</v>
       </c>
       <c r="C32" t="str">
-        <v>震惊</v>
+        <v>n./v.</v>
       </c>
       <c r="D32" t="str">
-        <v>shock(震惊)📢</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>propose</v>
-      </c>
-      <c r="C33" t="str">
-        <v>提议</v>
-      </c>
-      <c r="D33" t="str">
-        <v>propose(提议)📢</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>compass</v>
-      </c>
-      <c r="C34" t="str">
-        <v>指南针</v>
-      </c>
-      <c r="D34" t="str">
-        <v>compass(指南针)📢</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>thorough</v>
-      </c>
-      <c r="C35" t="str">
-        <v>彻底的</v>
-      </c>
-      <c r="D35" t="str">
-        <v>thorough(彻底的)📢</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>witness</v>
-      </c>
-      <c r="C36" t="str">
-        <v>见证</v>
-      </c>
-      <c r="D36" t="str">
-        <v>witness(见证)📢</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>theory</v>
-      </c>
-      <c r="C37" t="str">
-        <v>理论</v>
-      </c>
-      <c r="D37" t="str">
-        <v>theory(理论)📢</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>noisy</v>
-      </c>
-      <c r="C38" t="str">
-        <v>嘈杂</v>
-      </c>
-      <c r="D38" t="str">
-        <v>noisy(嘈杂)📢</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>until</v>
-      </c>
-      <c r="C39" t="str">
-        <v>直到</v>
-      </c>
-      <c r="D39" t="str">
-        <v>until(直到)📢</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>department</v>
-      </c>
-      <c r="C40" t="str">
-        <v>系</v>
-      </c>
-      <c r="D40" t="str">
-        <v>department(系)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>problem</v>
-      </c>
-      <c r="C41" t="str">
-        <v>问题</v>
-      </c>
-      <c r="D41" t="str">
-        <v>problem(问题)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>crowd</v>
-      </c>
-      <c r="C42" t="str">
         <v>人群</v>
-      </c>
-      <c r="D42" t="str">
-        <v>crowd(人群)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>witness</v>
-      </c>
-      <c r="C43" t="str">
-        <v>见证</v>
-      </c>
-      <c r="D43" t="str">
-        <v>witness(见证)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D32"/>
   </ignoredErrors>
 </worksheet>
 </file>